--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,6 +1091,322 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120448429</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blekatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>470288</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7016713</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120448427</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blekatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>470256</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7016734</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120448426</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Blekatjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>470246</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7016817</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hona födosök</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120448427</v>
+        <v>120448426</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470256</v>
+        <v>470246</v>
       </c>
       <c r="R7" t="n">
-        <v>7016734</v>
+        <v>7016817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hona födosök</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120448426</v>
+        <v>120448427</v>
       </c>
       <c r="B8" t="n">
         <v>57320</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470246</v>
+        <v>470256</v>
       </c>
       <c r="R8" t="n">
-        <v>7016817</v>
+        <v>7016734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Hona födosök</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120448429</v>
+        <v>120448426</v>
       </c>
       <c r="B6" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470288</v>
+        <v>470246</v>
       </c>
       <c r="R6" t="n">
-        <v>7016713</v>
+        <v>7016817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hona födosök</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120448426</v>
+        <v>120448429</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470246</v>
+        <v>470288</v>
       </c>
       <c r="R7" t="n">
-        <v>7016817</v>
+        <v>7016713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hona födosök</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120448426</v>
+        <v>120448429</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470246</v>
+        <v>470288</v>
       </c>
       <c r="R6" t="n">
-        <v>7016817</v>
+        <v>7016713</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hona födosök</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120448429</v>
+        <v>120448426</v>
       </c>
       <c r="B7" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470288</v>
+        <v>470246</v>
       </c>
       <c r="R7" t="n">
-        <v>7016713</v>
+        <v>7016817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hona födosök</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120448429</v>
+        <v>120448427</v>
       </c>
       <c r="B6" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470288</v>
+        <v>470256</v>
       </c>
       <c r="R6" t="n">
-        <v>7016713</v>
+        <v>7016734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120448427</v>
+        <v>120448429</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470256</v>
+        <v>470288</v>
       </c>
       <c r="R8" t="n">
-        <v>7016734</v>
+        <v>7016713</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120448427</v>
+        <v>120448426</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470256</v>
+        <v>470246</v>
       </c>
       <c r="R6" t="n">
-        <v>7016734</v>
+        <v>7016817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hona födosök</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120448426</v>
+        <v>120448429</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470246</v>
+        <v>470288</v>
       </c>
       <c r="R7" t="n">
-        <v>7016817</v>
+        <v>7016713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hona födosök</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120448429</v>
+        <v>120448427</v>
       </c>
       <c r="B8" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470288</v>
+        <v>470256</v>
       </c>
       <c r="R8" t="n">
-        <v>7016713</v>
+        <v>7016734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121200468</v>
+        <v>121200473</v>
       </c>
       <c r="B9" t="n">
-        <v>90687</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470245</v>
+        <v>470178</v>
       </c>
       <c r="R9" t="n">
-        <v>7016866</v>
+        <v>7016875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121200472</v>
+        <v>121200470</v>
       </c>
       <c r="B10" t="n">
-        <v>57348</v>
+        <v>90697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470175</v>
+        <v>470180</v>
       </c>
       <c r="R10" t="n">
-        <v>7016863</v>
+        <v>7016864</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121200481</v>
+        <v>121200467</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1630,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470401</v>
+        <v>470194</v>
       </c>
       <c r="R11" t="n">
-        <v>7016584</v>
+        <v>7016903</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121200467</v>
+        <v>121200472</v>
       </c>
       <c r="B12" t="n">
-        <v>90687</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470194</v>
+        <v>470175</v>
       </c>
       <c r="R12" t="n">
-        <v>7016903</v>
+        <v>7016863</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121200473</v>
+        <v>121200482</v>
       </c>
       <c r="B13" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1839,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470178</v>
+        <v>470363</v>
       </c>
       <c r="R13" t="n">
-        <v>7016875</v>
+        <v>7016562</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,11 +1903,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121200482</v>
+        <v>121200468</v>
       </c>
       <c r="B14" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,25 +1941,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470363</v>
+        <v>470245</v>
       </c>
       <c r="R14" t="n">
-        <v>7016562</v>
+        <v>7016866</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121200470</v>
+        <v>121200481</v>
       </c>
       <c r="B15" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470180</v>
+        <v>470401</v>
       </c>
       <c r="R15" t="n">
-        <v>7016864</v>
+        <v>7016584</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
         <v>121200469</v>
       </c>
       <c r="B16" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121214261</v>
+        <v>121214259</v>
       </c>
       <c r="B17" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470377</v>
+        <v>470307</v>
       </c>
       <c r="R17" t="n">
-        <v>7016640</v>
+        <v>7016661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121214259</v>
+        <v>121214261</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470307</v>
+        <v>470377</v>
       </c>
       <c r="R18" t="n">
-        <v>7016661</v>
+        <v>7016640</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
         <v>121200471</v>
       </c>
       <c r="B19" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -2031,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121200481</v>
+        <v>121200469</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470401</v>
+        <v>470192</v>
       </c>
       <c r="R15" t="n">
-        <v>7016584</v>
+        <v>7016852</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121200469</v>
+        <v>121200481</v>
       </c>
       <c r="B16" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,25 +2145,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470192</v>
+        <v>470401</v>
       </c>
       <c r="R16" t="n">
-        <v>7016852</v>
+        <v>7016584</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -2031,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121200469</v>
+        <v>121200481</v>
       </c>
       <c r="B15" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470192</v>
+        <v>470401</v>
       </c>
       <c r="R15" t="n">
-        <v>7016852</v>
+        <v>7016584</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121200481</v>
+        <v>121200469</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,25 +2145,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470401</v>
+        <v>470192</v>
       </c>
       <c r="R16" t="n">
-        <v>7016584</v>
+        <v>7016852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121200473</v>
+        <v>121200482</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470178</v>
+        <v>470363</v>
       </c>
       <c r="R9" t="n">
-        <v>7016875</v>
+        <v>7016562</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121200470</v>
+        <v>121200467</v>
       </c>
       <c r="B10" t="n">
         <v>90697</v>
@@ -1556,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470180</v>
+        <v>470194</v>
       </c>
       <c r="R10" t="n">
-        <v>7016864</v>
+        <v>7016903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121200467</v>
+        <v>121200469</v>
       </c>
       <c r="B11" t="n">
         <v>90697</v>
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470194</v>
+        <v>470192</v>
       </c>
       <c r="R11" t="n">
-        <v>7016903</v>
+        <v>7016852</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121200472</v>
+        <v>121200470</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470175</v>
+        <v>470180</v>
       </c>
       <c r="R12" t="n">
-        <v>7016863</v>
+        <v>7016864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1791,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121200482</v>
+        <v>121200473</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1839,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470363</v>
+        <v>470178</v>
       </c>
       <c r="R13" t="n">
-        <v>7016562</v>
+        <v>7016875</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121200468</v>
+        <v>121200472</v>
       </c>
       <c r="B14" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470245</v>
+        <v>470175</v>
       </c>
       <c r="R14" t="n">
-        <v>7016866</v>
+        <v>7016863</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,6 +2000,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,7 +2133,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121200469</v>
+        <v>121200468</v>
       </c>
       <c r="B16" t="n">
         <v>90697</v>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470192</v>
+        <v>470245</v>
       </c>
       <c r="R16" t="n">
-        <v>7016852</v>
+        <v>7016866</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121200482</v>
+        <v>121200470</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470363</v>
+        <v>470180</v>
       </c>
       <c r="R9" t="n">
-        <v>7016562</v>
+        <v>7016864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
         <v>121200467</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121200469</v>
+        <v>121200473</v>
       </c>
       <c r="B11" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470192</v>
+        <v>470178</v>
       </c>
       <c r="R11" t="n">
-        <v>7016852</v>
+        <v>7016875</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121200470</v>
+        <v>121200482</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,25 +1732,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470180</v>
+        <v>470363</v>
       </c>
       <c r="R12" t="n">
-        <v>7016864</v>
+        <v>7016562</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121200473</v>
+        <v>121200472</v>
       </c>
       <c r="B13" t="n">
         <v>57351</v>
@@ -1857,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470178</v>
+        <v>470175</v>
       </c>
       <c r="R13" t="n">
-        <v>7016875</v>
+        <v>7016863</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,7 +1902,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121200472</v>
+        <v>121200481</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1941,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470175</v>
+        <v>470401</v>
       </c>
       <c r="R14" t="n">
-        <v>7016863</v>
+        <v>7016584</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,11 +2005,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121200481</v>
+        <v>121200468</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470401</v>
+        <v>470245</v>
       </c>
       <c r="R15" t="n">
-        <v>7016584</v>
+        <v>7016866</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121200468</v>
+        <v>121200469</v>
       </c>
       <c r="B16" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470245</v>
+        <v>470192</v>
       </c>
       <c r="R16" t="n">
-        <v>7016866</v>
+        <v>7016852</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121214259</v>
+        <v>121214261</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470307</v>
+        <v>470377</v>
       </c>
       <c r="R17" t="n">
-        <v>7016661</v>
+        <v>7016640</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121214261</v>
+        <v>121214259</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470377</v>
+        <v>470307</v>
       </c>
       <c r="R18" t="n">
-        <v>7016640</v>
+        <v>7016661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121200470</v>
+        <v>121200467</v>
       </c>
       <c r="B9" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470180</v>
+        <v>470194</v>
       </c>
       <c r="R9" t="n">
-        <v>7016864</v>
+        <v>7016903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121200467</v>
+        <v>121200470</v>
       </c>
       <c r="B10" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470194</v>
+        <v>470180</v>
       </c>
       <c r="R10" t="n">
-        <v>7016903</v>
+        <v>7016864</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121200473</v>
+        <v>121200468</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>90710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470178</v>
+        <v>470245</v>
       </c>
       <c r="R11" t="n">
-        <v>7016875</v>
+        <v>7016866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121200482</v>
+        <v>121200473</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470363</v>
+        <v>470178</v>
       </c>
       <c r="R12" t="n">
-        <v>7016562</v>
+        <v>7016875</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121200472</v>
+        <v>121200482</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>98095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470175</v>
+        <v>470363</v>
       </c>
       <c r="R13" t="n">
-        <v>7016863</v>
+        <v>7016562</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121200481</v>
+        <v>121200472</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,25 +1936,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470401</v>
+        <v>470175</v>
       </c>
       <c r="R14" t="n">
-        <v>7016584</v>
+        <v>7016863</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,6 +2000,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121200468</v>
+        <v>121200481</v>
       </c>
       <c r="B15" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470245</v>
+        <v>470401</v>
       </c>
       <c r="R15" t="n">
-        <v>7016866</v>
+        <v>7016584</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
         <v>121200469</v>
       </c>
       <c r="B16" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>121214261</v>
       </c>
       <c r="B17" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>121214259</v>
       </c>
       <c r="B18" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121200467</v>
+        <v>121200473</v>
       </c>
       <c r="B9" t="n">
-        <v>90710</v>
+        <v>57354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470194</v>
+        <v>470178</v>
       </c>
       <c r="R9" t="n">
-        <v>7016903</v>
+        <v>7016875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,7 +1519,7 @@
         <v>121200470</v>
       </c>
       <c r="B10" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121200468</v>
+        <v>121200472</v>
       </c>
       <c r="B11" t="n">
-        <v>90710</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470245</v>
+        <v>470175</v>
       </c>
       <c r="R11" t="n">
-        <v>7016866</v>
+        <v>7016863</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121200473</v>
+        <v>121200469</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>90713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470178</v>
+        <v>470192</v>
       </c>
       <c r="R12" t="n">
-        <v>7016875</v>
+        <v>7016852</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1801,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,7 +1830,7 @@
         <v>121200482</v>
       </c>
       <c r="B13" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121200472</v>
+        <v>121200467</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>90713</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470175</v>
+        <v>470194</v>
       </c>
       <c r="R14" t="n">
-        <v>7016863</v>
+        <v>7016903</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,11 +2005,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2034,7 +2034,7 @@
         <v>121200481</v>
       </c>
       <c r="B15" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121200469</v>
+        <v>121200468</v>
       </c>
       <c r="B16" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470192</v>
+        <v>470245</v>
       </c>
       <c r="R16" t="n">
-        <v>7016852</v>
+        <v>7016866</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121214261</v>
+        <v>121214259</v>
       </c>
       <c r="B17" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470377</v>
+        <v>470307</v>
       </c>
       <c r="R17" t="n">
-        <v>7016640</v>
+        <v>7016661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121214259</v>
+        <v>121214261</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470307</v>
+        <v>470377</v>
       </c>
       <c r="R18" t="n">
-        <v>7016661</v>
+        <v>7016640</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
         <v>121200471</v>
       </c>
       <c r="B19" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121200473</v>
+        <v>121200482</v>
       </c>
       <c r="B9" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470178</v>
+        <v>470363</v>
       </c>
       <c r="R9" t="n">
-        <v>7016875</v>
+        <v>7016562</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121200470</v>
+        <v>121200469</v>
       </c>
       <c r="B10" t="n">
         <v>90713</v>
@@ -1556,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470180</v>
+        <v>470192</v>
       </c>
       <c r="R10" t="n">
-        <v>7016864</v>
+        <v>7016852</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121200472</v>
+        <v>121200481</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470175</v>
+        <v>470401</v>
       </c>
       <c r="R11" t="n">
-        <v>7016863</v>
+        <v>7016584</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121200469</v>
+        <v>121200472</v>
       </c>
       <c r="B12" t="n">
-        <v>90713</v>
+        <v>57354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470192</v>
+        <v>470175</v>
       </c>
       <c r="R12" t="n">
-        <v>7016852</v>
+        <v>7016863</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121200482</v>
+        <v>121200470</v>
       </c>
       <c r="B13" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1839,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470363</v>
+        <v>470180</v>
       </c>
       <c r="R13" t="n">
-        <v>7016562</v>
+        <v>7016864</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121200481</v>
+        <v>121200468</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,25 +2038,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470401</v>
+        <v>470245</v>
       </c>
       <c r="R15" t="n">
-        <v>7016584</v>
+        <v>7016866</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121200468</v>
+        <v>121200473</v>
       </c>
       <c r="B16" t="n">
-        <v>90713</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470245</v>
+        <v>470178</v>
       </c>
       <c r="R16" t="n">
-        <v>7016866</v>
+        <v>7016875</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,7 +2235,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121214259</v>
+        <v>121214261</v>
       </c>
       <c r="B17" t="n">
         <v>98098</v>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470307</v>
+        <v>470377</v>
       </c>
       <c r="R17" t="n">
-        <v>7016661</v>
+        <v>7016640</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121214261</v>
+        <v>121214259</v>
       </c>
       <c r="B18" t="n">
         <v>98098</v>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470377</v>
+        <v>470307</v>
       </c>
       <c r="R18" t="n">
-        <v>7016640</v>
+        <v>7016661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121200482</v>
+        <v>121200472</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>57355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470363</v>
+        <v>470175</v>
       </c>
       <c r="R9" t="n">
-        <v>7016562</v>
+        <v>7016863</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121200469</v>
+        <v>121200481</v>
       </c>
       <c r="B10" t="n">
-        <v>90713</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,25 +1528,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470192</v>
+        <v>470401</v>
       </c>
       <c r="R10" t="n">
-        <v>7016852</v>
+        <v>7016584</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121200481</v>
+        <v>121200482</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470401</v>
+        <v>470363</v>
       </c>
       <c r="R11" t="n">
-        <v>7016584</v>
+        <v>7016562</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121200472</v>
+        <v>121200469</v>
       </c>
       <c r="B12" t="n">
-        <v>57354</v>
+        <v>90719</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470175</v>
+        <v>470192</v>
       </c>
       <c r="R12" t="n">
-        <v>7016863</v>
+        <v>7016852</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,7 +1825,7 @@
         <v>121200470</v>
       </c>
       <c r="B13" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121200467</v>
+        <v>121200473</v>
       </c>
       <c r="B14" t="n">
-        <v>90713</v>
+        <v>57355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470194</v>
+        <v>470178</v>
       </c>
       <c r="R14" t="n">
-        <v>7016903</v>
+        <v>7016875</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,6 +2000,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2029,7 +2034,7 @@
         <v>121200468</v>
       </c>
       <c r="B15" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121200473</v>
+        <v>121200467</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>90719</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470178</v>
+        <v>470194</v>
       </c>
       <c r="R16" t="n">
-        <v>7016875</v>
+        <v>7016903</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,11 +2209,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2238,7 +2238,7 @@
         <v>121214261</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>121214259</v>
       </c>
       <c r="B18" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>121200471</v>
       </c>
       <c r="B19" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121200472</v>
+        <v>121200473</v>
       </c>
       <c r="B9" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470175</v>
+        <v>470178</v>
       </c>
       <c r="R9" t="n">
-        <v>7016863</v>
+        <v>7016875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121200481</v>
+        <v>121200467</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,25 +1528,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470401</v>
+        <v>470194</v>
       </c>
       <c r="R10" t="n">
-        <v>7016584</v>
+        <v>7016903</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121200482</v>
+        <v>121200468</v>
       </c>
       <c r="B11" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1630,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470363</v>
+        <v>470245</v>
       </c>
       <c r="R11" t="n">
-        <v>7016562</v>
+        <v>7016866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121200469</v>
+        <v>121200470</v>
       </c>
       <c r="B12" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470192</v>
+        <v>470180</v>
       </c>
       <c r="R12" t="n">
-        <v>7016852</v>
+        <v>7016864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121200470</v>
+        <v>121200482</v>
       </c>
       <c r="B13" t="n">
-        <v>90719</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470180</v>
+        <v>470363</v>
       </c>
       <c r="R13" t="n">
-        <v>7016864</v>
+        <v>7016562</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121200473</v>
+        <v>121200481</v>
       </c>
       <c r="B14" t="n">
-        <v>57355</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1936,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470178</v>
+        <v>470401</v>
       </c>
       <c r="R14" t="n">
-        <v>7016875</v>
+        <v>7016584</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,11 +2000,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121200468</v>
+        <v>121200469</v>
       </c>
       <c r="B15" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2071,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470245</v>
+        <v>470192</v>
       </c>
       <c r="R15" t="n">
-        <v>7016866</v>
+        <v>7016852</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121200467</v>
+        <v>121200472</v>
       </c>
       <c r="B16" t="n">
-        <v>90719</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470194</v>
+        <v>470175</v>
       </c>
       <c r="R16" t="n">
-        <v>7016903</v>
+        <v>7016863</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121214261</v>
+        <v>121214259</v>
       </c>
       <c r="B17" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470377</v>
+        <v>470307</v>
       </c>
       <c r="R17" t="n">
-        <v>7016640</v>
+        <v>7016661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121214259</v>
+        <v>121214261</v>
       </c>
       <c r="B18" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470307</v>
+        <v>470377</v>
       </c>
       <c r="R18" t="n">
-        <v>7016661</v>
+        <v>7016640</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2442,7 +2442,7 @@
         <v>121200471</v>
       </c>
       <c r="B19" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -2235,7 +2235,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121214259</v>
+        <v>121214261</v>
       </c>
       <c r="B17" t="n">
         <v>98105</v>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470307</v>
+        <v>470377</v>
       </c>
       <c r="R17" t="n">
-        <v>7016661</v>
+        <v>7016640</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121214261</v>
+        <v>121214259</v>
       </c>
       <c r="B18" t="n">
         <v>98105</v>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470377</v>
+        <v>470307</v>
       </c>
       <c r="R18" t="n">
-        <v>7016640</v>
+        <v>7016661</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115175175</v>
+        <v>120448429</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470251</v>
+        <v>470288</v>
       </c>
       <c r="R2" t="n">
-        <v>7016855</v>
+        <v>7016713</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115175174</v>
+        <v>115175176</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470305</v>
+        <v>470426</v>
       </c>
       <c r="R3" t="n">
-        <v>7016732</v>
+        <v>7016536</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115175176</v>
+        <v>121200467</v>
       </c>
       <c r="B4" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470426</v>
+        <v>470194</v>
       </c>
       <c r="R4" t="n">
-        <v>7016536</v>
+        <v>7016903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115175173</v>
+        <v>121200468</v>
       </c>
       <c r="B5" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>470428</v>
+        <v>470245</v>
       </c>
       <c r="R5" t="n">
-        <v>7016520</v>
+        <v>7016866</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120448427</v>
+        <v>121200469</v>
       </c>
       <c r="B6" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blekatjärnen, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>470256</v>
+        <v>470192</v>
       </c>
       <c r="R6" t="n">
-        <v>7016734</v>
+        <v>7016852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,17 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120448426</v>
+        <v>121200470</v>
       </c>
       <c r="B7" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blekatjärnen, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470246</v>
+        <v>470180</v>
       </c>
       <c r="R7" t="n">
-        <v>7016817</v>
+        <v>7016864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,17 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hona födosök</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120448429</v>
+        <v>115175174</v>
       </c>
       <c r="B8" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1323,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blekatjärnen, Jmt</t>
+          <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470288</v>
+        <v>470305</v>
       </c>
       <c r="R8" t="n">
-        <v>7016713</v>
+        <v>7016732</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,12 +1322,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121200473</v>
+        <v>115175175</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470178</v>
+        <v>470251</v>
       </c>
       <c r="R9" t="n">
-        <v>7016875</v>
+        <v>7016855</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,12 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1516,15 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121200467</v>
+        <v>120448426</v>
       </c>
       <c r="B10" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1532,34 +1472,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470194</v>
+        <v>470246</v>
       </c>
       <c r="R10" t="n">
-        <v>7016903</v>
+        <v>7016817</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,12 +1526,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hona födosök</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,15 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121200468</v>
+        <v>120448427</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,34 +1574,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rödön V, Jmt</t>
+          <t>Blekatjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470245</v>
+        <v>470256</v>
       </c>
       <c r="R11" t="n">
-        <v>7016866</v>
+        <v>7016734</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,12 +1628,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,15 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121200470</v>
+        <v>121200471</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,34 +1676,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödön V, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470180</v>
+        <v>470253</v>
       </c>
       <c r="R12" t="n">
-        <v>7016864</v>
+        <v>7016805</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1744,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Troligt tretå-bo</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,37 +1775,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121200482</v>
+        <v>121200472</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1810,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470363</v>
+        <v>470175</v>
       </c>
       <c r="R13" t="n">
-        <v>7016562</v>
+        <v>7016863</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,6 +1846,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,37 +1877,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121200481</v>
+        <v>121200473</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1912,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470401</v>
+        <v>470178</v>
       </c>
       <c r="R14" t="n">
-        <v>7016584</v>
+        <v>7016875</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,6 +1948,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,37 +1979,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121200469</v>
+        <v>121200481</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2014,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470192</v>
+        <v>470401</v>
       </c>
       <c r="R15" t="n">
-        <v>7016852</v>
+        <v>7016584</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,37 +2076,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121200472</v>
+        <v>121200482</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2111,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470175</v>
+        <v>470363</v>
       </c>
       <c r="R16" t="n">
-        <v>7016863</v>
+        <v>7016562</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,11 +2147,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,15 +2173,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121214261</v>
+        <v>121214259</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,10 +2208,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470377</v>
+        <v>470307</v>
       </c>
       <c r="R17" t="n">
-        <v>7016640</v>
+        <v>7016661</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,15 +2270,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121214259</v>
+        <v>121214261</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,10 +2305,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470307</v>
+        <v>470377</v>
       </c>
       <c r="R18" t="n">
-        <v>7016661</v>
+        <v>7016640</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,121 +2364,6 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>121200471</v>
-      </c>
-      <c r="B19" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Rödön V, Jmt</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>470253</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7016805</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Rödön</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Troligt tretå-bo</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39487-2024 artfynd.xlsx
+++ b/artfynd/A 39487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448429</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115175176</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200467</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200468</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200469</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200470</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115175174</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115175175</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448426</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120448427</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,6 +1827,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200471</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1874,6 +1934,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200472</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1976,6 +2041,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200473</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2073,6 +2143,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200481</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2170,6 +2245,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121200482</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2267,6 +2347,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121214259</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2364,8 +2449,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121214261</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>